--- a/Intersecciones/excels/LIMA-LIMA-LA_MOLINA.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-LA_MOLINA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-101109</t>
+          <t>I-12573</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-12.069465</t>
+          <t>-12.1170101</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-76.946654</t>
+          <t>-76.9377138</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Jr. Madre de Dios con Jr. Arequipa</t>
+          <t>Calle Río Rin / Pasaje Río Arauca</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-102274</t>
+          <t>I-12947</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,17 +560,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-12.068814</t>
+          <t>-12.102769</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-76.945372</t>
+          <t>-76.937551</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Jr. Madre de Dios con Jr. Cuzco</t>
+          <t>Avenida Las Lomas de la Molina Vieja / Jirón Posada del Marques</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-12911</t>
+          <t>I-12959</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -612,17 +612,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-12.099763</t>
+          <t>-12.103235</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-76.941199</t>
+          <t>-76.934284</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CALLE PASEO DEL PRADO CON LA AVENIDA LAS LOMAS DE LA MOLINA VIEJA</t>
+          <t>Calle Posada del Marquez / Calle Suspiro del Moro</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>l-12921</t>
+          <t>I-12823</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -664,17 +664,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-12.101074</t>
+          <t>-12.098422</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-76.93835</t>
+          <t>-76.948359</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CALLE ROCA DEL CASTILLO CON LA AVENIDA LAS LOMAS DE LA MOLINA VIEJA</t>
+          <t>Avenida Alameda de La Paz / Jirón Los Aromos</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>l-12934</t>
+          <t>I-91649</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -716,17 +716,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-12.101882</t>
+          <t>-12.069024</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-76.937905</t>
+          <t>-76.951756</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CALLE VEGAS DEL CONDADO CON LA AVENIDA LAS LOMAS DE LA MOLINA VIEJA</t>
+          <t>Calle Los Quimicos / Calle Los Forestales</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>l-12940</t>
+          <t>I-95981</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-12.102008</t>
+          <t>-12.065478</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-76.934322</t>
+          <t>-76.955302</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CALLE LOS MOLINOS DE SAN MIGUEL CON LA CALLE FUENTES DE ANDALUCIA</t>
+          <t>Calle Los Economos / Jirón Los Industriales</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -795,7 +795,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>l-12947</t>
+          <t>I-352534</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -820,17 +820,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-12.102769</t>
+          <t>-12.0745169</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-76.937551</t>
+          <t>-76.926991</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Jr. POSADA DEL MARQUES CON LA AVENIDA LAS LOMAS DE LA MOLINA VIEJA</t>
+          <t>Calle Monte Blanco / Calle s / n</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -839,734 +839,6 @@
         </is>
       </c>
       <c r="J8" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>l-12959</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-12.103235</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>-76.934284</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>CALLE CALESA DEL MARQUEZ CON LA CALLE SUSPIRO DEL MORO</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>l-132448</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-12.095693</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-76.924746</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Av. Rinconada del Lago - Ca. Huron</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>l-106392</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-12.0609116</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-76.9469668</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Galileo Galilei / Jr. Américo Vespucio</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>l-12542</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>-12.1170822</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>-76.9379773</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Calle Río Don / Calle Río Rin</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>l-12543</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>-12.1166395</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>-76.9381089</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Calle Río Don</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>l-12573</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>-12.1170101</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-76.9377138</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Calle Río Rin / Pasaje Río Arauca</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>l-138362</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>-12.060966</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-76.9469379</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Galileo Galilei</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>l-172907</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>-12.1167327</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-76.9382456</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>l-12823</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>-12.098422</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>-76.948359</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>ALAMEDA LA PAZ CON CA. LOS AROMOS</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>l-383201</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-12.09413</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-76.922691</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Av. Rinconada del Lago - Ca. Winnipeg</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>l-355666</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>-12.075714</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>-76.9619336</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>l-91649</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-12.069024</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-76.951756</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Ca. Los Químicos con Jr. Los Forestales</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>l-95981</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-12.065478</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-76.955302</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Jr. Los Industriales con Ca. Los Economos</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>l-97102</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>-12.069376</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>-76.943243</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Jr. Huancavelica con Jr. La Libertad</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
         <is>
           <t>150114</t>
         </is>

--- a/Intersecciones/excels/LIMA-LIMA-LA_MOLINA.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-LA_MOLINA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,7 +622,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Calle Posada del Marquez / Calle Suspiro del Moro</t>
+          <t>Posada del Marquez / Suspiro del Moro</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Calle Los Quimicos / Calle Los Forestales</t>
+          <t>Calle Los Quimicos / Los Forestales</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -839,6 +839,110 @@
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>150114</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>I-355773</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>150114</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>LA MOLINA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-12.0769805</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-76.9442034</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>150114</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I-355761</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>150114</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>LA MOLINA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-12.0766859</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-76.9717021</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>150114</t>
         </is>

--- a/Intersecciones/excels/LIMA-LIMA-LA_MOLINA.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-LA_MOLINA.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>150114</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LA_MOLINA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-12573</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-12.1170101</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>150114</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>150114</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LA_MOLINA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-12947</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-12.102769</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>150114</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>150114</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LA_MOLINA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-12959</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-12.103235</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>150114</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>150114</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LA_MOLINA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-12823</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-12.098422</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>150114</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>150114</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LA_MOLINA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-91649</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-12.069024</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>150114</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>150114</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LA_MOLINA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-95981</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-12.065478</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>150114</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>150114</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LA_MOLINA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-352534</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-12.0745169</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>150114</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>150114</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LA_MOLINA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-355773</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-12.0769805</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>150114</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>150114</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LA_MOLINA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-355761</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>LA MOLINA</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-12.0766859</t>
@@ -940,11 +895,6 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>150114</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/LIMA-LIMA-LA_MOLINA.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-LA_MOLINA.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/LIMA-LIMA-LA_MOLINA.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-LA_MOLINA.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/Intersecciones/excels/LIMA-LIMA-LA_MOLINA.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-LA_MOLINA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/LIMA-LIMA-LA_MOLINA.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-LA_MOLINA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,27 +486,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-12573</t>
+          <t>I-95981</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-12.1170101</t>
+          <t>-12.065478</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-76.9377138</t>
+          <t>-76.955302</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Calle Río Rin / Pasaje Río Arauca</t>
+          <t>Calle Los Economos / Jirón Los Industriales</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -533,22 +533,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-12947</t>
+          <t>I-91649</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-12.102769</t>
+          <t>-12.069024</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-76.937551</t>
+          <t>-76.951756</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida Las Lomas de la Molina Vieja / Jirón Posada del Marques</t>
+          <t>Calle Los Quimicos / Calle Los Forestales</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -580,22 +580,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-12959</t>
+          <t>I-6373</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-12.103235</t>
+          <t>-12.0661888</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-76.934284</t>
+          <t>-76.9433793</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Posada del Marquez / Suspiro del Moro</t>
+          <t>Avenida Javier Prado Este / Ricardo Palma</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-12823</t>
+          <t>I-355773</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-12.098422</t>
+          <t>-12.0769805</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-76.948359</t>
+          <t>-76.9442034</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Alameda de La Paz / Jirón Los Aromos</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-91649</t>
+          <t>I-355761</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-12.069024</t>
+          <t>-12.0766859</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-76.951756</t>
+          <t>-76.9717021</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Calle Los Quimicos / Los Forestales</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -721,22 +721,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-95981</t>
+          <t>I-352534</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-12.065478</t>
+          <t>-12.0745169</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-76.955302</t>
+          <t>-76.926991</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Calle Los Economos / Jirón Los Industriales</t>
+          <t>Calle Monte Blanco / Calle s / n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -768,22 +768,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-352534</t>
+          <t>I-12959</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-12.0745169</t>
+          <t>-12.103235</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-76.926991</t>
+          <t>-76.934284</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Calle Monte Blanco / Calle s / n</t>
+          <t>Calle Posada del Marquez / Calle Suspiro del Moro</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -815,22 +815,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-355773</t>
+          <t>I-12947</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-12.0769805</t>
+          <t>-12.102769</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-76.9442034</t>
+          <t>-76.937551</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Las Lomas de la Molina Vieja / Jirón Posada del Marques</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -862,27 +862,74 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-355761</t>
+          <t>I-12823</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-12.0766859</t>
+          <t>-12.098422</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-76.9717021</t>
+          <t>-76.948359</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Alameda de La Paz / Jirón Los Aromos</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>150114</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LA MOLINA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>I-12573</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-12.1170101</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-76.9377138</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Calle Río Rin / Pasaje Río Arauca</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
